--- a/INSTANCES/instances_xlsx/A_MTN_8/224FL_10A_2.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_8/224FL_10A_2.xlsx
@@ -7522,7 +7522,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -7624,7 +7624,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>1</v>
